--- a/evidence/AY-100-07-001.xlsx
+++ b/evidence/AY-100-07-001.xlsx
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-24T23:15:41.337Z</t>
+          <t>2026-10-25T02:17:10.780Z</t>
         </is>
       </c>
     </row>
